--- a/public/sap-reporting/expansion-150-downloads/EXT-FI24-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI24-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rdadfcb6e2b304d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R912e6128b8cd4406"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R0e8ebe4f1107421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re40c7d35d2704b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R19d43329e2e3422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R0dd198c93e70425f"/>
   </x:sheets>
 </x:workbook>
 </file>
